--- a/results/monthly_investor_report_2026-07-23.xlsx
+++ b/results/monthly_investor_report_2026-07-23.xlsx
@@ -630,7 +630,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-25 04:53</t>
+          <t>Son Güncelleme: 2026-07-26 05:17</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1004,16 +1004,16 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.1061157987449863</v>
+        <v>0.1061157987449862</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>10611.57987449863</v>
+        <v>10611.57987449862</v>
       </c>
       <c r="F21" s="7" t="n">
         <v>0.0439164979259993</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>466.0234255499948</v>
+        <v>466.0234255499947</v>
       </c>
       <c r="H21" s="8" t="n">
         <v>392.7735823446573</v>
@@ -1054,7 +1054,7 @@
         <v>0.0343566853834971</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>349.6367099705449</v>
+        <v>349.6367099705448</v>
       </c>
       <c r="H22" s="8" t="n">
         <v>205.009491886403</v>
@@ -1086,16 +1086,16 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>0.09680149841362548</v>
+        <v>0.09680149841362547</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>9680.149841362549</v>
+        <v>9680.149841362547</v>
       </c>
       <c r="F23" s="7" t="n">
         <v>0.0532805395405533</v>
       </c>
       <c r="G23" s="8" t="n">
-        <v>515.763606381198</v>
+        <v>515.7636063811979</v>
       </c>
       <c r="H23" s="8" t="n">
         <v>301.5015544434834</v>
@@ -1127,16 +1127,16 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>0.07961307892339649</v>
+        <v>0.07961307892339654</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>7961.307892339649</v>
+        <v>7961.307892339654</v>
       </c>
       <c r="F24" s="7" t="n">
         <v>0.0662461449400904</v>
       </c>
       <c r="G24" s="8" t="n">
-        <v>527.405956548618</v>
+        <v>527.4059565486184</v>
       </c>
       <c r="H24" s="8" t="n">
         <v>35.46334499104866</v>
@@ -1145,7 +1145,7 @@
         <v>31.34528912709862</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>1.150747422073201</v>
+        <v>1.150747422073205</v>
       </c>
       <c r="K24" s="9" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-25 04:53</t>
+          <t>Son Güncelleme: 2026-07-26 05:17</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1498,7 +1498,7 @@
         <v>314.5</v>
       </c>
       <c r="E9" s="18" t="n">
-        <v>-0.09857152200522271</v>
+        <v>-0.0985715220052225</v>
       </c>
       <c r="F9" s="18" t="n">
         <v>-0.0267076945339092</v>
@@ -1612,7 +1612,7 @@
         <v>22.55999946594238</v>
       </c>
       <c r="E11" s="18" t="n">
-        <v>-0.0480530189205196</v>
+        <v>-0.0480530189205198</v>
       </c>
       <c r="F11" s="18" t="n">
         <v>-0.0151488195452038</v>
@@ -1732,7 +1732,7 @@
         <v>0.0089213306645721</v>
       </c>
       <c r="G13" s="21" t="n">
-        <v>0.1846002415757828</v>
+        <v>0.184600241575783</v>
       </c>
       <c r="H13" s="20" t="n">
         <v>296.6181496934038</v>
@@ -1786,7 +1786,7 @@
         <v>-0.0609999645366716</v>
       </c>
       <c r="F14" s="18" t="n">
-        <v>-0.0154052729933271</v>
+        <v>-0.015405272993327</v>
       </c>
       <c r="G14" s="18" t="n">
         <v>0.0525822108985147</v>
@@ -1840,7 +1840,7 @@
         <v>286.25</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>0.0192863783331422</v>
+        <v>0.019286378333142</v>
       </c>
       <c r="F15" s="15" t="n">
         <v>0.0532805395405533</v>
@@ -1849,7 +1849,7 @@
         <v>0.084836584704717</v>
       </c>
       <c r="H15" s="14" t="n">
-        <v>291.770725797862</v>
+        <v>291.7707257978619</v>
       </c>
       <c r="I15" s="14" t="n">
         <v>301.5015544434834</v>
@@ -2014,7 +2014,7 @@
         <v>-0.0462686718992926</v>
       </c>
       <c r="F18" s="24" t="n">
-        <v>-0.0007077205736818</v>
+        <v>-0.0007077205736817</v>
       </c>
       <c r="G18" s="24" t="n">
         <v>0.1518716549814833</v>
@@ -2155,7 +2155,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-25 04:53</t>
+          <t>Son Güncelleme: 2026-07-26 05:17</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2289,7 +2289,7 @@
         </is>
       </c>
       <c r="E5" s="18" t="n">
-        <v>0.4269510377015333</v>
+        <v>0.4269510377015331</v>
       </c>
       <c r="F5" s="18" t="n">
         <v>0.2406311637080866</v>
@@ -2524,7 +2524,7 @@
         <v>0.0280762215956702</v>
       </c>
       <c r="K10" s="18" t="n">
-        <v>-0.0154052729933271</v>
+        <v>-0.015405272993327</v>
       </c>
     </row>
     <row r="11">
@@ -2593,7 +2593,7 @@
         <v>-0.054054054054054</v>
       </c>
       <c r="F12" s="18" t="n">
-        <v>-0.08933220103328331</v>
+        <v>-0.0893322010332832</v>
       </c>
       <c r="G12" s="18" t="n">
         <v>-0.004739336492891</v>
@@ -2607,7 +2607,7 @@
         </is>
       </c>
       <c r="J12" s="18" t="n">
-        <v>0.0227482826335469</v>
+        <v>0.022748282633547</v>
       </c>
       <c r="K12" s="18" t="n">
         <v>-0.0223463826050375</v>
@@ -2650,7 +2650,7 @@
         </is>
       </c>
       <c r="J13" s="15" t="n">
-        <v>0.0287839640868978</v>
+        <v>0.0287839640868977</v>
       </c>
       <c r="K13" s="15" t="n">
         <v>0.0662461449400904</v>
@@ -2822,10 +2822,10 @@
         </is>
       </c>
       <c r="J17" s="24" t="n">
-        <v>0.019334221948612</v>
+        <v>0.0193342219486119</v>
       </c>
       <c r="K17" s="24" t="n">
-        <v>-0.0007077205736818</v>
+        <v>-0.0007077205736817</v>
       </c>
     </row>
     <row r="18">
@@ -2865,7 +2865,7 @@
         </is>
       </c>
       <c r="J18" s="26" t="n">
-        <v>0.0159758845365429</v>
+        <v>0.015975884536543</v>
       </c>
       <c r="K18" s="26" t="n">
         <v>0.0384313523279102</v>
@@ -2908,7 +2908,7 @@
         </is>
       </c>
       <c r="J19" s="26" t="n">
-        <v>0.0280471682847775</v>
+        <v>0.0280471682847774</v>
       </c>
       <c r="K19" s="26" t="n">
         <v>0.06497451176343599</v>
@@ -2987,7 +2987,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-25 04:53</t>
+          <t>Son Güncelleme: 2026-07-26 05:17</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3106,7 +3106,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-25 04:53</t>
+          <t>Son Güncelleme: 2026-07-26 05:17</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3357,7 +3357,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-25 04:53</t>
+          <t>Son Güncelleme: 2026-07-26 05:17</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3482,7 +3482,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-25 04:53</t>
+          <t>Son Güncelleme: 2026-07-26 05:17</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>

--- a/results/monthly_investor_report_2026-07-23.xlsx
+++ b/results/monthly_investor_report_2026-07-23.xlsx
@@ -630,7 +630,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-26 05:17</t>
+          <t>Son Güncelleme: 2026-07-27 05:35</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1244,7 +1244,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-26 05:17</t>
+          <t>Son Güncelleme: 2026-07-27 05:35</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2155,7 +2155,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-26 05:17</t>
+          <t>Son Güncelleme: 2026-07-27 05:35</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2987,7 +2987,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-26 05:17</t>
+          <t>Son Güncelleme: 2026-07-27 05:35</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3106,7 +3106,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-26 05:17</t>
+          <t>Son Güncelleme: 2026-07-27 05:35</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3357,7 +3357,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-26 05:17</t>
+          <t>Son Güncelleme: 2026-07-27 05:35</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3482,7 +3482,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-26 05:17</t>
+          <t>Son Güncelleme: 2026-07-27 05:35</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
